--- a/basedatos_partidas/salida/descompuestos/12.01.01.280.xlsx
+++ b/basedatos_partidas/salida/descompuestos/12.01.01.280.xlsx
@@ -558,10 +558,10 @@
         <v>0.15</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="H20" t="n">
         <v>0.02</v>
@@ -736,7 +736,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
     </row>
   </sheetData>
